--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.44498723557754</v>
+        <v>2.67231042578135</v>
       </c>
       <c r="D2" t="n">
-        <v>15.85218890785304</v>
+        <v>2.575980697526119</v>
       </c>
       <c r="E2" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F2" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.78826178206489</v>
+        <v>5.815592539585546</v>
       </c>
       <c r="D3" t="n">
-        <v>6.500420234065819</v>
+        <v>1.056318288035696</v>
       </c>
       <c r="E3" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F3" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.283333911460819</v>
+        <v>1.346041760612383</v>
       </c>
       <c r="D4" t="n">
-        <v>8.644357532361287</v>
+        <v>1.404708099008709</v>
       </c>
       <c r="E4" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F4" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.435985427538485</v>
+        <v>1.533347631975004</v>
       </c>
       <c r="D5" t="n">
-        <v>10.68093083961088</v>
+        <v>1.735651261436768</v>
       </c>
       <c r="E5" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F5" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.78250094811493</v>
+        <v>4.514656404068676</v>
       </c>
       <c r="D6" t="n">
-        <v>3.928077535775138</v>
+        <v>0.63831259956346</v>
       </c>
       <c r="E6" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F6" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.91919662682853</v>
+        <v>2.911869451859636</v>
       </c>
       <c r="D7" t="n">
-        <v>7.291319505882428</v>
+        <v>1.184839419705895</v>
       </c>
       <c r="E7" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F7" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.16105844473349</v>
+        <v>1.976171997269192</v>
       </c>
       <c r="D8" t="n">
-        <v>10.38808628636671</v>
+        <v>1.68806402153459</v>
       </c>
       <c r="E8" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F8" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.38026422834599</v>
+        <v>6.886792937106224</v>
       </c>
       <c r="D9" t="n">
-        <v>15.85112018474125</v>
+        <v>2.575807030020453</v>
       </c>
       <c r="E9" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F9" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.25683851139806</v>
+        <v>5.566736258102185</v>
       </c>
       <c r="D10" t="n">
-        <v>5.507995198900505</v>
+        <v>0.8950492198213321</v>
       </c>
       <c r="E10" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F10" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>59.03943269019621</v>
+        <v>9.593907812156884</v>
       </c>
       <c r="D11" t="n">
-        <v>31.9098210886556</v>
+        <v>5.185345926906535</v>
       </c>
       <c r="E11" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F11" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.63226289090799</v>
+        <v>7.577742719772548</v>
       </c>
       <c r="D12" t="n">
-        <v>17.26267650163207</v>
+        <v>2.805184931515211</v>
       </c>
       <c r="E12" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F12" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63.50798136825713</v>
+        <v>10.32004697234179</v>
       </c>
       <c r="D13" t="n">
-        <v>55.29544664575091</v>
+        <v>8.985510079934524</v>
       </c>
       <c r="E13" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F13" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>46.3820843864027</v>
+        <v>7.537088712790438</v>
       </c>
       <c r="D14" t="n">
-        <v>40.38873605350878</v>
+        <v>6.563169608695177</v>
       </c>
       <c r="E14" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F14" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.60486054493784</v>
+        <v>7.410789838552398</v>
       </c>
       <c r="D15" t="n">
-        <v>44.23212903835203</v>
+        <v>7.187720968732206</v>
       </c>
       <c r="E15" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F15" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>45.61688283958035</v>
+        <v>7.412743461431807</v>
       </c>
       <c r="D16" t="n">
-        <v>34.36177457623462</v>
+        <v>5.583788368638126</v>
       </c>
       <c r="E16" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F16" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.43559969638568</v>
+        <v>2.995784950662673</v>
       </c>
       <c r="D17" t="n">
-        <v>17.78216649281617</v>
+        <v>2.889602055082628</v>
       </c>
       <c r="E17" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F17" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>7.930952023559342</v>
+        <v>1.288779703828393</v>
       </c>
       <c r="D18" t="n">
-        <v>4.712693011997577</v>
+        <v>0.7658126144496062</v>
       </c>
       <c r="E18" t="n">
-        <v>17.70120463533242</v>
+        <v>2.876445753241519</v>
       </c>
       <c r="F18" t="n">
-        <v>15.32462550910535</v>
+        <v>2.49025164522962</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
